--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -476,12 +476,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEMO-NOT-IN-VAULT-0001</t>
+          <t>628f6dd1-eccb-4e61-8a0a-74523f3e3cd1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DEMO-NOT-IN-VAULT-0002</t>
+          <t>9a2dd38b-f30a-4fbd-a48e-f99142c0a8d8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8b43885d-7a9f-400e-ae04-363d14a09d22</t>
+          <t>67d3b1ae-7dd2-49fb-b15f-3fce45051998</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26T00:41:02+00:00</t>
+          <t>2026-09-26T01:00:45+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,27 +429,62 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>ToD Conclusion</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ToE Conclusion</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ToE Basis</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Items Tested</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Exceptions Noted</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Preliminary Deficiency</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Evidence Quote</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Vault ID</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Quote Verified in Vault</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Legacy Severity</t>
         </is>
       </c>
     </row>
@@ -461,61 +496,170 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[DEMO DATA — synthetic evidence] The sample password policy meets the length requirement in the test step.</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PasswordPolicy: MinimumPasswordLength=14</t>
+          <t>Single point-in-time configuration read: design and implementation evidence only. Operating effectiveness for the period would rely on change-management ITGCs over IAM configuration or on AWS Config history; neither was tested in this demo.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>628f6dd1-eccb-4e61-8a0a-74523f3e3cd1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No exception</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[DEMO DATA — synthetic evidence] Design and implementation: at the time of the read, the sample password policy meets the length requirement in the test step. Operating effectiveness over the period was not tested.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MinimumPasswordLength=14</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>94c05e48-0fca-4892-be7b-8c01c058bde1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CTRL-03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>No evidence tool covers this control.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[DEMO DATA — no evidence] No available evidence tool covers this control (review sign-offs are held outside AWS), so it was not tested. This is a scope limitation, not a deficiency.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>n/a (no evidence)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CTRL-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Control Deficiency</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[DEMO DATA — synthetic evidence] One sample bucket does not block public ACLs; remediation would be needed.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BlockPublicAcls: false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>9a2dd38b-f30a-4fbd-a48e-f99142c0a8d8</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ineffective</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Not performed: the control is not implemented on one bucket, so operating effectiveness was not tested.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[DEMO DATA — synthetic evidence] One of three sample buckets does not block public ACLs; the control is not implemented as designed.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bucket demo-analytics-exports: BlockPublicAcls: false</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8b12663a-1eba-4cd7-8c57-325a88fac320</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -528,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67d3b1ae-7dd2-49fb-b15f-3fce45051998</t>
+          <t>c057c748-a29c-4821-8cfd-33d034d284d7</t>
         </is>
       </c>
     </row>
@@ -599,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26T01:00:45+00:00</t>
+          <t>2026-09-26T22:31:08+00:00</t>
         </is>
       </c>
     </row>
@@ -611,7 +755,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Theme: [DEMO DATA] AWS Cloud Security</t>
+          <t>Theme: [DEMO DATA] AWS IAM and S3 access controls</t>
         </is>
       </c>
     </row>
@@ -624,6 +768,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>Quote Verified in Vault is re-checked at export time: the quote must appear verbatim in the stored evidence and the record's digest must match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Preliminary Deficiency is a fieldwork flag only. Deficiencies are classified at engagement level in the report's deficiency evaluation.</t>
         </is>
       </c>
     </row>

--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>94c05e48-0fca-4892-be7b-8c01c058bde1</t>
+          <t>9e5fdde5-c99c-4b48-b195-02c5c43d737e</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8b12663a-1eba-4cd7-8c57-325a88fac320</t>
+          <t>e475844d-75b6-4bd3-9a24-1dfe63ab9967</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c057c748-a29c-4821-8cfd-33d034d284d7</t>
+          <t>c85898be-ad5a-4e0e-86f2-d2af3b62524b</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26T22:31:08+00:00</t>
+          <t>2026-09-26T22:51:25+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -531,17 +531,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[DEMO DATA — synthetic evidence] Design and implementation: at the time of the read, the sample password policy meets the length requirement in the test step. Operating effectiveness over the period was not tested.</t>
+          <t>[DEMO DATA — synthetic evidence] Design and implementation: at the time of the read, the password policy meets the minimum length (14) and the complexity rules in the test step (symbols, numbers, uppercase). Operating effectiveness over the period was not tested.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MinimumPasswordLength=14</t>
+          <t>MinimumPasswordLength=14, RequireSymbols=true, RequireNumbers=true, RequireUppercaseCharacters=true</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9e5fdde5-c99c-4b48-b195-02c5c43d737e</t>
+          <t>be449040-284b-424f-a401-a02198a85193</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[DEMO DATA — no evidence] No available evidence tool covers this control (review sign-offs are held outside AWS), so it was not tested. This is a scope limitation, not a deficiency.</t>
+          <t>[DEMO DATA — no evidence] No available evidence tool covers this control (review sign-offs are held outside AWS), so it was not tested. It is a key control: before Gate 3 the auditor must either extend testing (for example, inspect the review sign-offs) or report it as a scope limitation.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -641,17 +641,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[DEMO DATA — synthetic evidence] One of three sample buckets does not block public ACLs; the control is not implemented as designed.</t>
+          <t>[DEMO DATA — synthetic evidence] All three buckets in the population were tested (full population from ListBuckets). One bucket is public through an ACL granting AllUsers READ, with Block Public Access off at both account and bucket level; for that bucket the control is not implemented as designed.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bucket demo-analytics-exports: BlockPublicAcls: false</t>
+          <t>Bucket demo-analytics-exports: Verdict=PUBLIC, Reasons=ACL grants AllUsers READ</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>e475844d-75b6-4bd3-9a24-1dfe63ab9967</t>
+          <t>93d469c5-13ea-4718-8767-e554d2a60b7e</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c85898be-ad5a-4e0e-86f2-d2af3b62524b</t>
+          <t>713374ef-8db5-44be-9b4f-5470f1528ab0</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26T22:51:25+00:00</t>
+          <t>2026-09-27T00:39:38+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,36 @@
           <t>Legacy Severity</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer Decision</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewed By (declared)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewed At (UTC)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer Rationale</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>AI Draft (where the record differs)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Scope Limitation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -541,7 +571,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>be449040-284b-424f-a401-a02198a85193</t>
+          <t>447cf8d2-43e1-4122-a446-2823744bb011</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -550,6 +580,28 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Signed off</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Ivan In-Charge (demo)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-09-27T15:54:46.368767+00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>[DEMO DATA] Design evidence agrees to the test step; the ToE gap is stated in the working paper.</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -597,6 +649,32 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Signed off</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Ivan In-Charge (demo)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-09-27T15:54:46.376811+00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[DEMO DATA] Agreed that no evidence covers this control; it will be reported as a scope limitation.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[DEMO DATA] CTRL-03 was not tested: its evidence is held outside AWS. Reported as a scope limitation; no conclusion is given on it.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,7 +729,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>93d469c5-13ea-4718-8767-e554d2a60b7e</t>
+          <t>a9ba3adf-534f-404a-a062-6b0d707f8355</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -660,6 +738,28 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Signed off</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Ivan In-Charge (demo)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-09-27T15:54:46.385776+00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>[DEMO DATA] Exception agreed to the verified vault quote.</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -672,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,7 +795,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AWS IAM and S3 access controls audit</t>
+          <t>AWS S3 and IAM security audit</t>
         </is>
       </c>
     </row>
@@ -707,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>713374ef-8db5-44be-9b4f-5470f1528ab0</t>
+          <t>26cdd98f-b68e-420d-b33e-285ca381b76d</t>
         </is>
       </c>
     </row>
@@ -743,7 +843,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-27T00:39:38+00:00</t>
+          <t>2026-09-27T15:54:46+00:00</t>
         </is>
       </c>
     </row>
@@ -755,7 +855,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Theme: [DEMO DATA] AWS IAM and S3 access controls</t>
+          <t>Theme: [DEMO DATA] AWS S3 and IAM security</t>
         </is>
       </c>
     </row>
@@ -780,6 +880,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>Preliminary Deficiency is a fieldwork flag only. Deficiencies are classified at engagement level in the report's deficiency evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ToD / ToE / Result show the conclusion of record: the AI draft, unless a reviewer's challenge withdrew a conclusion (the draft is then shown under 'AI Draft'). Identities are declared, not authenticated.</t>
         </is>
       </c>
     </row>

--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>447cf8d2-43e1-4122-a446-2823744bb011</t>
+          <t>1c024f31-f92d-45db-a3ec-4f172b4efb59</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46.368767+00:00</t>
+          <t>2026-09-27T21:00:30.237347+00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46.376811+00:00</t>
+          <t>2026-09-27T21:00:30.246029+00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>a9ba3adf-534f-404a-a062-6b0d707f8355</t>
+          <t>9ad68af5-7aa3-4628-b5af-ce987d163cdc</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46.385776+00:00</t>
+          <t>2026-09-27T21:00:30.254831+00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26cdd98f-b68e-420d-b33e-285ca381b76d</t>
+          <t>4231ece5-08b7-41d7-bcce-acf273d10ac9</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46+00:00</t>
+          <t>2026-09-27T21:00:30+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1c024f31-f92d-45db-a3ec-4f172b4efb59</t>
+          <t>444ef197-202d-4aa1-8dda-2d72050145cd</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-27T21:00:30.237347+00:00</t>
+          <t>2026-09-27T21:10:13.535770+00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-27T21:00:30.246029+00:00</t>
+          <t>2026-09-27T21:10:13.543729+00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>9ad68af5-7aa3-4628-b5af-ce987d163cdc</t>
+          <t>6d4f9f6d-ac46-4fea-a2cd-9f628a3b544e</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-27T21:00:30.254831+00:00</t>
+          <t>2026-09-27T21:10:13.550578+00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4231ece5-08b7-41d7-bcce-acf273d10ac9</t>
+          <t>1a08dd3c-3c3d-4776-8599-a377a68523b5</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-27T21:00:30+00:00</t>
+          <t>2026-09-27T21:10:13+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/sample-run/working-papers.xlsx
+++ b/docs/sample-run/working-papers.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>447cf8d2-43e1-4122-a446-2823744bb011</t>
+          <t>444ef197-202d-4aa1-8dda-2d72050145cd</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46.368767+00:00</t>
+          <t>2026-09-27T21:10:13.535770+00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46.376811+00:00</t>
+          <t>2026-09-27T21:10:13.543729+00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>a9ba3adf-534f-404a-a062-6b0d707f8355</t>
+          <t>6d4f9f6d-ac46-4fea-a2cd-9f628a3b544e</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46.385776+00:00</t>
+          <t>2026-09-27T21:10:13.550578+00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26cdd98f-b68e-420d-b33e-285ca381b76d</t>
+          <t>1a08dd3c-3c3d-4776-8599-a377a68523b5</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-27T15:54:46+00:00</t>
+          <t>2026-09-27T21:10:13+00:00</t>
         </is>
       </c>
     </row>
